--- a/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
+++ b/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8</f>
+              <f>'30日跟踪'!$A$8:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8</f>
+              <f>'30日跟踪'!$D$8:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -708,6 +708,26 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>第1/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>7.900000095367432</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-9.714284624372205</v>
+      </c>
+      <c r="D9" s="6">
+        <f>B9/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>第2/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
+++ b/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$9</f>
+              <f>'30日跟踪'!$A$8:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$9</f>
+              <f>'30日跟踪'!$D$8:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -728,6 +728,26 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>第2/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>7.65500020980835</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-3.101264336727672</v>
+      </c>
+      <c r="D10" s="6">
+        <f>B10/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>第3/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
+++ b/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$10</f>
+              <f>'30日跟踪'!$A$8:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$10</f>
+              <f>'30日跟踪'!$D$8:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -748,6 +748,26 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>第3/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>7.039999961853027</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-8.033967747869198</v>
+      </c>
+      <c r="D11" s="6">
+        <f>B11/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>第4/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
+++ b/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$11</f>
+              <f>'30日跟踪'!$A$8:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$11</f>
+              <f>'30日跟踪'!$D$8:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -768,6 +768,26 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>第4/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>7.610000133514404</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>8.096593391334972</v>
+      </c>
+      <c r="D12" s="6">
+        <f>B12/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>第5/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
+++ b/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$12</f>
+              <f>'30日跟踪'!$A$8:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$12</f>
+              <f>'30日跟踪'!$D$8:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -788,6 +788,46 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>第5/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>7.630000114440918</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.2628118341080343</v>
+      </c>
+      <c r="D13" s="6">
+        <f>B13/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>第6/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>7.619999885559082</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-0.131064596747632</v>
+      </c>
+      <c r="D14" s="6">
+        <f>B14/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>第7/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
+++ b/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$14</f>
+              <f>'30日跟踪'!$A$8:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$14</f>
+              <f>'30日跟踪'!$D$8:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -828,6 +828,26 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>第7/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>7.619999885559082</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6">
+        <f>B15/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>第8/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
+++ b/data/BOLL/EXCLE/ONDS_1_20260827.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$15</f>
+              <f>'30日跟踪'!$A$8:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$15</f>
+              <f>'30日跟踪'!$D$8:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -848,6 +848,26 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>第8/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>7.289999961853027</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-4.330707725225147</v>
+      </c>
+      <c r="D16" s="6">
+        <f>B16/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>第9/30个交易日</t>
         </is>
       </c>
     </row>
